--- a/data/trans_camb/P6901-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6901-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 8,8</t>
+          <t>-17,3; 11,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 11,36</t>
+          <t>-19,92; 10,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 13,45</t>
+          <t>-15,67; 13,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 25,67</t>
+          <t>-9,32; 25,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 23,41</t>
+          <t>-14,7; 22,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 17,81</t>
+          <t>-17,07; 16,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 11,59</t>
+          <t>-12,28; 11,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,65; 10,14</t>
+          <t>-13,32; 10,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 10,19</t>
+          <t>-11,1; 10,98</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,89; 12,17</t>
+          <t>-20,65; 17,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 15,76</t>
+          <t>-24,68; 15,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,15; 18,28</t>
+          <t>-18,34; 18,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 41,31</t>
+          <t>-9,84; 38,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 35,88</t>
+          <t>-16,29; 32,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 26,87</t>
+          <t>-19,1; 25,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 15,88</t>
+          <t>-14,57; 15,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 13,7</t>
+          <t>-16,42; 14,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-12,01; 13,98</t>
+          <t>-13,62; 15,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 16,36</t>
+          <t>-7,63; 17,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 14,93</t>
+          <t>-8,6; 15,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 11,85</t>
+          <t>-11,81; 11,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 19,27</t>
+          <t>-12,35; 18,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 29,0</t>
+          <t>-0,64; 27,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 16,98</t>
+          <t>-9,89; 16,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 13,73</t>
+          <t>-3,7; 15,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 17,12</t>
+          <t>-1,39; 17,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 10,57</t>
+          <t>-5,25; 11,5</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 24,89</t>
+          <t>-9,76; 26,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 22,36</t>
+          <t>-11,09; 23,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 18,1</t>
+          <t>-15,47; 17,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,33; 29,67</t>
+          <t>-14,24; 28,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 45,15</t>
+          <t>-0,49; 43,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 26,76</t>
+          <t>-11,43; 25,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 20,07</t>
+          <t>-4,75; 21,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 25,41</t>
+          <t>-1,83; 25,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 15,7</t>
+          <t>-6,86; 16,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 8,73</t>
+          <t>-16,31; 10,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 14,15</t>
+          <t>-7,95; 14,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 11,79</t>
+          <t>-17,82; 10,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 3,94</t>
+          <t>-28,61; 3,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 14,07</t>
+          <t>-13,5; 14,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 16,01</t>
+          <t>-17,97; 15,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 3,56</t>
+          <t>-15,88; 4,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 11,69</t>
+          <t>-6,02; 11,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,3; 13,43</t>
+          <t>-12,0; 13,03</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 11,15</t>
+          <t>-20,38; 13,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 20,62</t>
+          <t>-9,66; 20,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 16,06</t>
+          <t>-21,98; 14,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,29; 5,07</t>
+          <t>-31,39; 3,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-13,03; 18,25</t>
+          <t>-14,7; 18,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 21,14</t>
+          <t>-20,3; 23,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,83; 4,56</t>
+          <t>-19,21; 5,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 15,66</t>
+          <t>-7,08; 15,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 18,0</t>
+          <t>-14,32; 17,29</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 9,71</t>
+          <t>-15,57; 9,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 5,67</t>
+          <t>-19,88; 4,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 5,02</t>
+          <t>-18,36; 5,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 14,68</t>
+          <t>-15,61; 14,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 19,05</t>
+          <t>-10,05; 18,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 11,64</t>
+          <t>-18,63; 10,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 7,54</t>
+          <t>-11,65; 7,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 7,04</t>
+          <t>-10,92; 7,8</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 4,97</t>
+          <t>-14,53; 4,12</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 13,8</t>
+          <t>-19,56; 13,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,19; 7,65</t>
+          <t>-25,59; 5,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 6,75</t>
+          <t>-22,9; 8,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,35; 22,9</t>
+          <t>-19,74; 21,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 30,03</t>
+          <t>-12,45; 27,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 16,99</t>
+          <t>-22,94; 15,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 10,59</t>
+          <t>-14,8; 11,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 9,82</t>
+          <t>-13,89; 11,08</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 7,12</t>
+          <t>-18,46; 5,73</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 5,26</t>
+          <t>-6,76; 5,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 5,86</t>
+          <t>-6,64; 5,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 3,93</t>
+          <t>-8,88; 3,84</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 8,13</t>
+          <t>-7,69; 7,15</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 14,08</t>
+          <t>-0,84; 14,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 8,01</t>
+          <t>-7,43; 8,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,71</t>
+          <t>-5,57; 4,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 7,34</t>
+          <t>-2,14; 7,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 5,43</t>
+          <t>-5,19; 4,5</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 7,15</t>
+          <t>-8,69; 7,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 8,13</t>
+          <t>-8,56; 7,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 5,39</t>
+          <t>-11,83; 5,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 10,99</t>
+          <t>-9,46; 9,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 19,53</t>
+          <t>-0,96; 19,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 10,79</t>
+          <t>-9,13; 12,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 6,4</t>
+          <t>-7,0; 5,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 9,93</t>
+          <t>-2,75; 9,87</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 7,37</t>
+          <t>-6,72; 5,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6901-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6901-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,3; 11,96</t>
+          <t>-16,59; 11,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 10,79</t>
+          <t>-19,38; 9,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 13,0</t>
+          <t>-14,72; 14,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 25,04</t>
+          <t>-10,1; 25,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 22,34</t>
+          <t>-13,06; 23,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,07; 16,94</t>
+          <t>-15,04; 17,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 11,13</t>
+          <t>-11,32; 11,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 10,47</t>
+          <t>-13,47; 10,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 10,98</t>
+          <t>-10,2; 10,11</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,55%</t>
+          <t>-1,26%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,14%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>-0,09%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 17,17</t>
+          <t>-20,14; 16,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,68; 15,01</t>
+          <t>-24,33; 13,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,34; 18,32</t>
+          <t>-17,35; 19,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 38,11</t>
+          <t>-10,44; 39,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-16,29; 32,57</t>
+          <t>-14,92; 33,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 25,34</t>
+          <t>-16,62; 24,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 15,39</t>
+          <t>-13,41; 17,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 14,45</t>
+          <t>-16,77; 14,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 15,37</t>
+          <t>-12,06; 14,24</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>4,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 17,0</t>
+          <t>-6,32; 17,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 15,52</t>
+          <t>-9,93; 14,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 11,39</t>
+          <t>-6,99; 15,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 18,64</t>
+          <t>-12,18; 18,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 27,67</t>
+          <t>0,9; 29,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 16,98</t>
+          <t>-8,51; 17,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 15,14</t>
+          <t>-4,14; 15,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 17,27</t>
+          <t>-2,24; 17,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 11,5</t>
+          <t>-3,55; 13,17</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 26,05</t>
+          <t>-8,44; 27,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 23,38</t>
+          <t>-13,14; 22,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,47; 17,2</t>
+          <t>-9,58; 22,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,24; 28,65</t>
+          <t>-14,39; 27,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 43,19</t>
+          <t>1,4; 46,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 25,57</t>
+          <t>-9,99; 27,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 21,96</t>
+          <t>-5,68; 22,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 25,54</t>
+          <t>-2,85; 25,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 16,94</t>
+          <t>-4,62; 20,34</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-3,3</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,23</t>
+          <t>-11,7</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,51</t>
+          <t>-3,55</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 10,64</t>
+          <t>-18,54; 9,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 14,94</t>
+          <t>-8,04; 14,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,82; 10,72</t>
+          <t>-12,25; 14,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 3,01</t>
+          <t>-26,6; 5,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 14,28</t>
+          <t>-12,76; 13,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 15,67</t>
+          <t>-25,11; 3,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 4,33</t>
+          <t>-17,39; 4,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 11,49</t>
+          <t>-6,11; 11,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,0; 13,03</t>
+          <t>-14,01; 6,05</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-4,25%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-3,77%</t>
+          <t>-13,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-0,64%</t>
+          <t>-4,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 13,78</t>
+          <t>-22,84; 12,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 20,77</t>
+          <t>-9,54; 21,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 14,28</t>
+          <t>-14,63; 20,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 3,59</t>
+          <t>-30,34; 5,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 18,35</t>
+          <t>-13,9; 17,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,3; 23,28</t>
+          <t>-28,37; 4,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 5,81</t>
+          <t>-21,3; 5,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 15,38</t>
+          <t>-7,29; 14,72</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 17,29</t>
+          <t>-16,55; 8,03</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-5,98</t>
+          <t>-4,55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,4</t>
+          <t>2,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-4,41</t>
+          <t>-1,3</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-15,57; 9,43</t>
+          <t>-15,1; 8,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 4,06</t>
+          <t>-20,7; 4,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 5,87</t>
+          <t>-16,04; 7,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,61; 14,17</t>
+          <t>-14,42; 14,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 18,37</t>
+          <t>-9,45; 19,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 10,51</t>
+          <t>-8,57; 14,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 7,99</t>
+          <t>-10,66; 7,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 7,8</t>
+          <t>-10,4; 7,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,53; 4,12</t>
+          <t>-9,39; 6,82</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-7,87%</t>
+          <t>-5,99%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-3,26%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-5,87%</t>
+          <t>-1,73%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 13,19</t>
+          <t>-19,18; 12,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-25,59; 5,43</t>
+          <t>-26,11; 6,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,9; 8,09</t>
+          <t>-20,28; 10,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 21,17</t>
+          <t>-18,94; 21,99</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 27,22</t>
+          <t>-11,78; 29,11</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 15,61</t>
+          <t>-10,48; 22,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 11,34</t>
+          <t>-13,4; 11,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 11,08</t>
+          <t>-13,53; 10,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,46; 5,73</t>
+          <t>-11,94; 9,75</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,66</t>
+          <t>-7,46; 5,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,08</t>
+          <t>-6,98; 6,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 3,84</t>
+          <t>-6,31; 5,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 7,15</t>
+          <t>-8,41; 8,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 14,08</t>
+          <t>-1,15; 14,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 8,84</t>
+          <t>-7,17; 6,45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 4,38</t>
+          <t>-5,67; 4,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 7,26</t>
+          <t>-2,77; 7,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 4,5</t>
+          <t>-4,46; 4,5</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-3,1%</t>
+          <t>-0,29%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>-0,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-0,74%</t>
+          <t>0,19%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 7,84</t>
+          <t>-9,69; 7,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 7,08</t>
+          <t>-8,9; 8,34</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 5,18</t>
+          <t>-8,24; 7,97</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 9,64</t>
+          <t>-10,44; 10,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 19,26</t>
+          <t>-1,39; 20,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 12,14</t>
+          <t>-8,59; 8,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 5,99</t>
+          <t>-7,1; 5,96</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 9,87</t>
+          <t>-3,54; 9,96</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 5,99</t>
+          <t>-5,66; 6,14</t>
         </is>
       </c>
     </row>
